--- a/artfynd/A 26751-2025 artfynd.xlsx
+++ b/artfynd/A 26751-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>125785776</v>
       </c>
       <c r="B3" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26751-2025 artfynd.xlsx
+++ b/artfynd/A 26751-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125785732</v>
       </c>
       <c r="B2" t="n">
-        <v>80071</v>
+        <v>80072</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125785776</v>
       </c>
       <c r="B3" t="n">
-        <v>98352</v>
+        <v>98355</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125785697</v>
       </c>
       <c r="B4" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>125785796</v>
       </c>
       <c r="B5" t="n">
-        <v>80071</v>
+        <v>80072</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 26751-2025 artfynd.xlsx
+++ b/artfynd/A 26751-2025 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125785697</v>
+        <v>125785796</v>
       </c>
       <c r="B4" t="n">
-        <v>78968</v>
+        <v>80072</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,13 +904,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>380692</v>
+        <v>380685</v>
       </c>
       <c r="R4" t="n">
-        <v>6839601</v>
+        <v>6839649</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125785796</v>
+        <v>125785697</v>
       </c>
       <c r="B5" t="n">
-        <v>80072</v>
+        <v>78968</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>380685</v>
+        <v>380692</v>
       </c>
       <c r="R5" t="n">
-        <v>6839649</v>
+        <v>6839601</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>

--- a/artfynd/A 26751-2025 artfynd.xlsx
+++ b/artfynd/A 26751-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125785732</v>
       </c>
       <c r="B2" t="n">
-        <v>80072</v>
+        <v>80076</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125785776</v>
       </c>
       <c r="B3" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125785796</v>
       </c>
       <c r="B4" t="n">
-        <v>80072</v>
+        <v>80076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>125785697</v>
       </c>
       <c r="B5" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 26751-2025 artfynd.xlsx
+++ b/artfynd/A 26751-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>125785776</v>
       </c>
       <c r="B3" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125785796</v>
+        <v>125785697</v>
       </c>
       <c r="B4" t="n">
-        <v>80076</v>
+        <v>78972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,13 +904,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>380685</v>
+        <v>380692</v>
       </c>
       <c r="R4" t="n">
-        <v>6839649</v>
+        <v>6839601</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125785697</v>
+        <v>125785796</v>
       </c>
       <c r="B5" t="n">
-        <v>78972</v>
+        <v>80076</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>380692</v>
+        <v>380685</v>
       </c>
       <c r="R5" t="n">
-        <v>6839601</v>
+        <v>6839649</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>

--- a/artfynd/A 26751-2025 artfynd.xlsx
+++ b/artfynd/A 26751-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125785732</v>
       </c>
       <c r="B2" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125785776</v>
       </c>
       <c r="B3" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125785697</v>
       </c>
       <c r="B4" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>125785796</v>
       </c>
       <c r="B5" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 26751-2025 artfynd.xlsx
+++ b/artfynd/A 26751-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>125785776</v>
       </c>
       <c r="B3" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125785697</v>
+        <v>125785796</v>
       </c>
       <c r="B4" t="n">
-        <v>78973</v>
+        <v>80077</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,13 +904,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>380692</v>
+        <v>380685</v>
       </c>
       <c r="R4" t="n">
-        <v>6839601</v>
+        <v>6839649</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125785796</v>
+        <v>125785697</v>
       </c>
       <c r="B5" t="n">
-        <v>80077</v>
+        <v>78973</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>380685</v>
+        <v>380692</v>
       </c>
       <c r="R5" t="n">
-        <v>6839649</v>
+        <v>6839601</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>

--- a/artfynd/A 26751-2025 artfynd.xlsx
+++ b/artfynd/A 26751-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>125785776</v>
       </c>
       <c r="B3" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26751-2025 artfynd.xlsx
+++ b/artfynd/A 26751-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125785732</v>
       </c>
       <c r="B2" t="n">
-        <v>80077</v>
+        <v>80081</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125785776</v>
       </c>
       <c r="B3" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125785796</v>
       </c>
       <c r="B4" t="n">
-        <v>80077</v>
+        <v>80081</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>125785697</v>
       </c>
       <c r="B5" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 26751-2025 artfynd.xlsx
+++ b/artfynd/A 26751-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>125785776</v>
       </c>
       <c r="B3" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125785796</v>
+        <v>125785697</v>
       </c>
       <c r="B4" t="n">
-        <v>80081</v>
+        <v>78977</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,13 +904,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>380685</v>
+        <v>380692</v>
       </c>
       <c r="R4" t="n">
-        <v>6839649</v>
+        <v>6839601</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125785697</v>
+        <v>125785796</v>
       </c>
       <c r="B5" t="n">
-        <v>78977</v>
+        <v>80081</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>380692</v>
+        <v>380685</v>
       </c>
       <c r="R5" t="n">
-        <v>6839601</v>
+        <v>6839649</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>

--- a/artfynd/A 26751-2025 artfynd.xlsx
+++ b/artfynd/A 26751-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125785732</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125785796</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125785697</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,8 +1080,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125785776</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>